--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251003_184421.xlsx
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
